--- a/策划/excel/19_Equipment.xlsx
+++ b/策划/excel/19_Equipment.xlsx
@@ -2254,8 +2254,10 @@
       <c r="D6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>24</v>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F6" s="3" t="s">
         <v>25</v>
@@ -2280,8 +2282,10 @@
       <c r="D7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>30</v>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F7" s="3" t="s">
         <v>25</v>
@@ -2306,8 +2310,10 @@
       <c r="D8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>34</v>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F8" s="3" t="s">
         <v>25</v>
@@ -2332,8 +2338,10 @@
       <c r="D9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>38</v>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210022,"target":"SELF","params":{"event":"ON_HAND_READY","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210038,"target":"SELF","params":{"count":1},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F9" s="3" t="s">
         <v>25</v>
@@ -2358,8 +2366,10 @@
       <c r="D10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>42</v>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F10" s="3" t="s">
         <v>25</v>
@@ -2384,8 +2394,10 @@
       <c r="D11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>46</v>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":4,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_BEFORE_CARD_PLAYED","scope":"COMBAT","limit":0,"filter":{"type":"ATTACK"}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.attackCount","cmp":"==","rhs":2}]},"children":[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":8,"timing":"NEXT_CARD"},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F11" s="4" t="s">
         <v>47</v>
@@ -2410,8 +2422,10 @@
       <c r="D12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>52</v>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_BLOCK_CARD_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":5,"timing":"NEXT_CARD"},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_ATTACK_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":5,"timing":"NEXT_CARD"},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F12" s="4" t="s">
         <v>47</v>
@@ -2436,8 +2450,10 @@
       <c r="D13" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>57</v>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_CARD_DAMAGE_DEALT","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.amount","cmp":"&gt;=","rhs":10},{"lhs":"@heavyHitRewarded","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"heavyHitRewarded","value":1,"scope":"TURN"},"children":[],"elseEffects":[]},{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F13" s="4" t="s">
         <v>47</v>
@@ -2462,8 +2478,10 @@
       <c r="D14" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>62</v>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_ATTACK_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.requiredDiceCount","cmp":"&gt;=","rhs":2}]},"children":[{"type":210034,"target":"SELF","params":{"name":"heavyAttackCount","operator":"ADD","value":1,"scope":"TURN"},"children":[],"elseEffects":[]},{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@heavyAttackCount","cmp":"&gt;=","rhs":2},{"lhs":"@heavyAttackRewarded","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"heavyAttackRewarded","value":1,"scope":"TURN"},"children":[],"elseEffects":[]},{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F14" s="4" t="s">
         <v>47</v>
@@ -2488,8 +2506,10 @@
       <c r="D15" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>67</v>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_ENERGY_SPENT","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210034,"target":"SELF","params":{"name":"spentEnergy","operator":"ADD","value":"@event.spent","scope":"TURN"},"children":[],"elseEffects":[]},{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@spentEnergy","cmp":"&gt;=","rhs":3},{"lhs":"@energyDamageTriggered","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"energyDamageTriggered","value":1,"scope":"TURN"},"children":[],"elseEffects":[]},{"type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F15" s="4" t="s">
         <v>47</v>
@@ -2514,8 +2534,10 @@
       <c r="D16" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>72</v>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210039,"target":"SELF","params":{"amount":6},"children":[],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F16" s="4" t="s">
         <v>73</v>
@@ -2540,8 +2562,10 @@
       <c r="D17" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>78</v>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_DAMAGE_TAKEN","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@hitGuardScheduled","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"hitGuardScheduled","value":1,"scope":"TURN"},"children":[],"elseEffects":[]},{"type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"type":210002,"target":"SELF","params":{"amount":5,"scale":false},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F17" s="4" t="s">
         <v>73</v>
@@ -2566,8 +2590,10 @@
       <c r="D18" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>83</v>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_HAND_READY","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210038,"target":"SELF","params":{"count":1},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_BLOCK_CARD_PLAYED","scope":"COMBAT","limit":0,"filter":{"type":"SKILL"}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@blockSkillDrawn","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"blockSkillDrawn","value":1,"scope":"TURN"},"children":[],"elseEffects":[]},{"type":210038,"target":"SELF","params":{"count":1},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F18" s="4" t="s">
         <v>73</v>
@@ -2592,8 +2618,10 @@
       <c r="D19" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>88</v>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_END","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210002,"target":"SELF","params":{"amount":"min(@self.energy, 2) * 3","scale":false},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F19" s="4" t="s">
         <v>73</v>
@@ -2618,8 +2646,10 @@
       <c r="D20" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>93</v>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":12,"duration":"RUN"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@self.hp","cmp":"&lt;","rhs":"@self.maxHp * 0.5"},{"lhs":"@lowHpTriggered","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"lowHpTriggered","value":1,"scope":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":12,"scale":false},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_HP_LOSS","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@self.hp","cmp":"&lt;","rhs":"@self.maxHp * 0.5"},{"lhs":"@lowHpTriggered","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"lowHpTriggered","value":1,"scope":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":12,"scale":false},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F20" s="4" t="s">
         <v>73</v>
@@ -2644,8 +2674,10 @@
       <c r="D21" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>98</v>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":false},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F21" s="4" t="s">
         <v>73</v>
@@ -2670,8 +2702,10 @@
       <c r="D22" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>103</v>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_ENERGY_SPENT","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.current","cmp":"==","rhs":0},{"lhs":"@emptyEnergyGuarded","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"emptyEnergyGuarded","value":1,"scope":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":10,"scale":false},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F22" s="4" t="s">
         <v>73</v>
@@ -2696,8 +2730,10 @@
       <c r="D23" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>108</v>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":2},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_CARD_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.cardCount","cmp":"==","rhs":3}]},"children":[{"type":210040,"target":"SELF","params":{"count":1,"scope":"TURN"},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F23" s="4" t="s">
         <v>73</v>
@@ -2722,8 +2758,10 @@
       <c r="D24" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>42</v>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F24" s="4" t="s">
         <v>47</v>
@@ -2748,8 +2786,10 @@
       <c r="D25" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>117</v>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":3},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
+        </is>
       </c>
       <c r="F25" s="4" t="s">
         <v>73</v>

--- a/策划/excel/19_Equipment.xlsx
+++ b/策划/excel/19_Equipment.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowWidth="25935" windowHeight="15735"/>
   </bookViews>
   <sheets>
     <sheet name="19_Equipment" sheetId="1" r:id="rId1"/>
@@ -106,7 +106,7 @@
     <t>仍带着巨狼血腥气息的獠牙，适合锻成凶狠的武器。</t>
   </si>
   <si>
-    <t>[{"type":"MODIFY_CARD_VALUE","target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"}}]</t>
+    <t>[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>Component</t>
@@ -124,7 +124,7 @@
     <t>尼达维利尔出产的黑铁，沉重，却能承受惊人的冲击。</t>
   </si>
   <si>
-    <t>[{"type":"MODIFY_CARD_VALUE","target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"}}]</t>
+    <t>[{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>世界树种</t>
@@ -136,7 +136,7 @@
     <t>从世界树根须旁拾得的种子，内部仍蕴藏着旺盛的生命力。</t>
   </si>
   <si>
-    <t>[{"type":"MODIFY_STAT","target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"}}]</t>
+    <t>[{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>渡鸦之羽</t>
@@ -148,7 +148,7 @@
     <t>一根漆黑的神鸦羽毛，握在手中时，思绪似乎变得更加敏锐。</t>
   </si>
   <si>
-    <t>[{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_HAND_READY","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":"DRAW","target":"SELF","params":{"count":1}}]}]</t>
+    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_HAND_READY","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210038,"target":"SELF","params":{"count":1},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>原初卢恩</t>
@@ -160,7 +160,7 @@
     <t>刻着古老符文的碎片，触碰时能感到微弱而稳定的神力流动。</t>
   </si>
   <si>
-    <t>[{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":"GAIN_ENERGY","target":"SELF","params":{"amount":1}}]}]</t>
+    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>芬里尔双牙</t>
@@ -234,7 +234,7 @@
     <t>以两枚巨狼獠牙锻成的双刃，越是连续进攻，越能激起野兽般的杀意。</t>
   </si>
   <si>
-    <t>[{"type":"MODIFY_CARD_VALUE","target":"SELF","params":{"kind":"DAMAGE","amount":4,"timing":"COMBAT"}},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_BEFORE_CARD_PLAYED","scope":"COMBAT","limit":0,"filter":{"type":"ATTACK"}},"children":[{"type":"IF","target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.attackCount","cmp":"==","rhs":2}]},"children":[{"type":"MODIFY_CARD_VALUE","target":"SELF","params":{"kind":"DAMAGE","amount":8,"timing":"NEXT_CARD"}}],"elseEffects":[]}]}]</t>
+    <t>[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":4,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_BEFORE_CARD_PLAYED","scope":"COMBAT","limit":0,"filter":{"type":"ATTACK"}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.attackCount","cmp":"==","rhs":2}]},"children":[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":8,"timing":"NEXT_CARD"},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>Weapon</t>
@@ -332,7 +332,7 @@
     <t>矮人以狼牙与黑铁铸成的战斧，攻守之间的节奏就是它真正的锋刃。</t>
   </si>
   <si>
-    <t>[{"type":"MODIFY_CARD_VALUE","target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"}},{"type":"MODIFY_CARD_VALUE","target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"}},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_BLOCK_CARD_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":"MODIFY_CARD_VALUE","target":"SELF","params":{"kind":"DAMAGE","amount":5,"timing":"NEXT_CARD"}}]},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_ATTACK_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":"MODIFY_CARD_VALUE","target":"SELF","params":{"kind":"BLOCK","amount":5,"timing":"NEXT_CARD"}}]}]</t>
+    <t>[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_BLOCK_CARD_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":5,"timing":"NEXT_CARD"},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_ATTACK_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":5,"timing":"NEXT_CARD"},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>[190001,190002]</t>
@@ -427,7 +427,7 @@
     <t>据说这柄沉重的屠刀曾被用于猎杀霜巨人，唯有真正的重击才能唤醒它。</t>
   </si>
   <si>
-    <t>[{"type":"MODIFY_CARD_VALUE","target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"}},{"type":"MODIFY_STAT","target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"}},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_CARD_DAMAGE_DEALT","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":"IF","target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.amount","cmp":"&gt;=","rhs":10},{"lhs":"@heavyHitRewarded","cmp":"==","rhs":0}]},"children":[{"type":"SET_VARIABLE","target":"SELF","params":{"name":"heavyHitRewarded","value":1,"scope":"TURN"}},{"type":"GAIN_ENERGY","target":"SELF","params":{"amount":1}}],"elseEffects":[]}]}]</t>
+    <t>[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_CARD_DAMAGE_DEALT","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.amount","cmp":"&gt;=","rhs":10},{"lhs":"@heavyHitRewarded","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"heavyHitRewarded","value":1,"scope":"TURN"},"children":[],"elseEffects":[]},{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>[190001,190003]</t>
@@ -504,7 +504,7 @@
     <t>黑羽缠绕在枪柄上，持有者总能在攻势中更快看见下一步。</t>
   </si>
   <si>
-    <t>[{"type":"MODIFY_CARD_VALUE","target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"}},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":"GAIN_ENERGY","target":"SELF","params":{"amount":1}}]},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_ATTACK_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":"IF","target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.requiredDiceCount","cmp":"&gt;=","rhs":2}]},"children":[{"type":"MODIFY_VARIABLE","target":"SELF","params":{"name":"heavyAttackCount","operator":"ADD","value":1,"scope":"TURN"}},{"type":"IF","target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@heavyAttackCount","cmp":"&gt;=","rhs":2},{"lhs":"@heavyAttackRewarded","cmp":"==","rhs":0}]},"children":[{"type":"SET_VARIABLE","target":"SELF","params":{"name":"heavyAttackRewarded","value":1,"scope":"TURN"}},{"type":"GAIN_ENERGY","target":"SELF","params":{"amount":1}}],"elseEffects":[]}],"elseEffects":[]}]}]</t>
+    <t>[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_ATTACK_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.requiredDiceCount","cmp":"&gt;=","rhs":2}]},"children":[{"type":210034,"target":"SELF","params":{"name":"heavyAttackCount","operator":"ADD","value":1,"scope":"TURN"},"children":[],"elseEffects":[]},{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@heavyAttackCount","cmp":"&gt;=","rhs":2},{"lhs":"@heavyAttackRewarded","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"heavyAttackRewarded","value":1,"scope":"TURN"},"children":[],"elseEffects":[]},{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>[190001,190004]</t>
@@ -635,7 +635,7 @@
     <t>原初卢恩被嵌入狼牙战锤，挥舞时会在空气中留下短暂的雷鸣。</t>
   </si>
   <si>
-    <t>[{"type":"MODIFY_CARD_VALUE","target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"}},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":"GAIN_ENERGY","target":"SELF","params":{"amount":1}}]},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_ENERGY_SPENT","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":"MODIFY_VARIABLE","target":"SELF","params":{"name":"spentEnergy","operator":"ADD","value":"@event.spent","scope":"TURN"}},{"type":"IF","target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@spentEnergy","cmp":"&gt;=","rhs":3},{"lhs":"@energyDamageTriggered","cmp":"==","rhs":0}]},"children":[{"type":"SET_VARIABLE","target":"SELF","params":{"name":"energyDamageTriggered","value":1,"scope":"TURN"}},{"type":"DAMAGE","target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false}}],"elseEffects":[]}]}]</t>
+    <t>[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_ENERGY_SPENT","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210034,"target":"SELF","params":{"name":"spentEnergy","operator":"ADD","value":"@event.spent","scope":"TURN"},"children":[],"elseEffects":[]},{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@spentEnergy","cmp":"&gt;=","rhs":3},{"lhs":"@energyDamageTriggered","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"energyDamageTriggered","value":1,"scope":"TURN"},"children":[],"elseEffects":[]},{"type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>[190001,190005]</t>
@@ -694,7 +694,7 @@
     <t>两块尼达维利尔黑铁熔铸为一体，厚重得几乎像一堵可以背在身上的城墙。</t>
   </si>
   <si>
-    <t>[{"type":"MODIFY_CARD_VALUE","target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"}},{"type":"RETAIN_BLOCK","target":"SELF","params":{"amount":6}}]</t>
+    <t>[{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210039,"target":"SELF","params":{"amount":6},"children":[],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>Armor</t>
@@ -774,7 +774,7 @@
     <t>黑铁护住躯体，世界树的生命力则让每一次受创都转化为新的防护。</t>
   </si>
   <si>
-    <t>[{"type":"MODIFY_CARD_VALUE","target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"}},{"type":"MODIFY_STAT","target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"}},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_DAMAGE_TAKEN","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":"IF","target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@hitGuardScheduled","cmp":"==","rhs":0}]},"children":[{"type":"SET_VARIABLE","target":"SELF","params":{"name":"hitGuardScheduled","value":1,"scope":"TURN"}},{"type":"SCHEDULE","target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"type":"BLOCK","target":"SELF","params":{"amount":5,"scale":false}}]}],"elseEffects":[]}]}]</t>
+    <t>[{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_DAMAGE_TAKEN","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@hitGuardScheduled","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"hitGuardScheduled","value":1,"scope":"TURN"},"children":[],"elseEffects":[]},{"type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"type":210002,"target":"SELF","params":{"amount":5,"scale":false},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>[190002,190003]</t>
@@ -789,7 +789,7 @@
     <t>披风边缘缝着神鸦黑羽，行动时仿佛总有女武神在耳边提醒下一次防守。</t>
   </si>
   <si>
-    <t>[{"type":"MODIFY_CARD_VALUE","target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"}},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_HAND_READY","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":"DRAW","target":"SELF","params":{"count":1}}]},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_BLOCK_CARD_PLAYED","scope":"COMBAT","limit":0,"filter":{"type":"SKILL"}},"children":[{"type":"IF","target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@blockSkillDrawn","cmp":"==","rhs":0}]},"children":[{"type":"SET_VARIABLE","target":"SELF","params":{"name":"blockSkillDrawn","value":1,"scope":"TURN"}},{"type":"DRAW","target":"SELF","params":{"count":1}}],"elseEffects":[]}]}]</t>
+    <t>[{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_HAND_READY","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210038,"target":"SELF","params":{"count":1},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_BLOCK_CARD_PLAYED","scope":"COMBAT","limit":0,"filter":{"type":"SKILL"}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@blockSkillDrawn","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"blockSkillDrawn","value":1,"scope":"TURN"},"children":[],"elseEffects":[]},{"type":210038,"target":"SELF","params":{"count":1},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>[190002,190004]</t>
@@ -920,7 +920,7 @@
     <t>符文沿盾面缓慢流动，未被挥霍的力量会在回合末凝成坚固的屏障。</t>
   </si>
   <si>
-    <t>[{"type":"MODIFY_CARD_VALUE","target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"}},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":"GAIN_ENERGY","target":"SELF","params":{"amount":1}}]},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_TURN_END","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":"BLOCK","target":"SELF","params":{"amount":"min(@self.energy, 2) * 3","scale":false}}]}]</t>
+    <t>[{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_END","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210002,"target":"SELF","params":{"amount":"min(@self.energy, 2) * 3","scale":false},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>[190002,190005]</t>
@@ -935,7 +935,7 @@
     <t>两枚世界树种在巨人的血中生根，凝成一颗异常沉重而顽强的生命核心。</t>
   </si>
   <si>
-    <t>[{"type":"MODIFY_STAT","target":"SELF","params":{"stat":"MAX_HP","amount":12,"duration":"RUN"}},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":"IF","target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@self.hp","cmp":"&lt;","rhs":"@self.maxHp * 0.5"},{"lhs":"@lowHpTriggered","cmp":"==","rhs":0}]},"children":[{"type":"SET_VARIABLE","target":"SELF","params":{"name":"lowHpTriggered","value":1,"scope":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":12,"scale":false}}],"elseEffects":[]}]},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_HP_LOSS","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":"IF","target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@self.hp","cmp":"&lt;","rhs":"@self.maxHp * 0.5"},{"lhs":"@lowHpTriggered","cmp":"==","rhs":0}]},"children":[{"type":"SET_VARIABLE","target":"SELF","params":{"name":"lowHpTriggered","value":1,"scope":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":12,"scale":false}}],"elseEffects":[]}]}]</t>
+    <t>[{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":12,"duration":"RUN"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@self.hp","cmp":"&lt;","rhs":"@self.maxHp * 0.5"},{"lhs":"@lowHpTriggered","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"lowHpTriggered","value":1,"scope":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":12,"scale":false},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_HP_LOSS","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@self.hp","cmp":"&lt;","rhs":"@self.maxHp * 0.5"},{"lhs":"@lowHpTriggered","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"lowHpTriggered","value":1,"scope":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":12,"scale":false},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>[190003,190003]</t>
@@ -1030,7 +1030,7 @@
     <t>以世界树纤维与渡鸦羽编成的旅衣，既给予耐力，也让思绪保持清醒。</t>
   </si>
   <si>
-    <t>[{"type":"MODIFY_STAT","target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"}},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":"GAIN_ENERGY","target":"SELF","params":{"amount":1}},{"type":"BLOCK","target":"SELF","params":{"amount":4,"scale":false}}]}]</t>
+    <t>[{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":false},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>[190003,190004]</t>
@@ -1045,7 +1045,7 @@
     <t>战死者的誓言被刻进腰带，每当力量倾尽，它便替佩戴者挡下下一次冲击。</t>
   </si>
   <si>
-    <t>[{"type":"MODIFY_STAT","target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"}},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":"GAIN_ENERGY","target":"SELF","params":{"amount":1}}]},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_ENERGY_SPENT","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":"IF","target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.current","cmp":"==","rhs":0},{"lhs":"@emptyEnergyGuarded","cmp":"==","rhs":0}]},"children":[{"type":"SET_VARIABLE","target":"SELF","params":{"name":"emptyEnergyGuarded","value":1,"scope":"COMBAT"}},{"type":"BLOCK","target":"SELF","params":{"amount":10,"scale":false}}],"elseEffects":[]}]}]</t>
+    <t>[{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_ENERGY_SPENT","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.current","cmp":"==","rhs":0},{"lhs":"@emptyEnergyGuarded","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"emptyEnergyGuarded","value":1,"scope":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":10,"scale":false},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>[190003,190005]</t>
@@ -1086,7 +1086,7 @@
     <t>两根来自奥丁神鸦的羽毛被缝在一起，思想与记忆令连贯的行动变得更加轻盈。</t>
   </si>
   <si>
-    <t>[{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":"GAIN_ENERGY","target":"SELF","params":{"amount":2}}]},{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_CARD_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":"IF","target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.cardCount","cmp":"==","rhs":3}]},"children":[{"type":"FREE_DICE","target":"SELF","params":{"count":1,"scope":"TURN"}}],"elseEffects":[]}]}]</t>
+    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":2},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_CARD_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.cardCount","cmp":"==","rhs":3}]},"children":[{"type":210040,"target":"SELF","params":{"count":1,"scope":"TURN"},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>[190004,190004]</t>
@@ -1183,7 +1183,7 @@
     <t>两枚原初卢恩彼此共鸣，如同一颗被封入战甲的雷霆心脏。</t>
   </si>
   <si>
-    <t>[{"type":"REGISTER_TRIGGER","target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":"GAIN_ENERGY","target":"SELF","params":{"amount":3}}]}]</t>
+    <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":3},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
   </si>
   <si>
     <t>[190005,190005]</t>
@@ -1199,7 +1199,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1211,13 +1211,6 @@
       <sz val="11"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1679,148 +1672,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1829,17 +1822,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2254,10 +2247,8 @@
       <c r="D6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]}]</t>
-        </is>
+      <c r="E6" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>25</v>
@@ -2282,10 +2273,8 @@
       <c r="D7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]}]</t>
-        </is>
+      <c r="E7" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>25</v>
@@ -2310,10 +2299,8 @@
       <c r="D8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"},"children":[],"elseEffects":[]}]</t>
-        </is>
+      <c r="E8" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>25</v>
@@ -2338,10 +2325,8 @@
       <c r="D9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210022,"target":"SELF","params":{"event":"ON_HAND_READY","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210038,"target":"SELF","params":{"count":1},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+      <c r="E9" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>25</v>
@@ -2366,10 +2351,8 @@
       <c r="D10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+      <c r="E10" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>25</v>
@@ -2394,10 +2377,8 @@
       <c r="D11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":4,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_BEFORE_CARD_PLAYED","scope":"COMBAT","limit":0,"filter":{"type":"ATTACK"}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.attackCount","cmp":"==","rhs":2}]},"children":[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":8,"timing":"NEXT_CARD"},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+      <c r="E11" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>47</v>
@@ -2422,10 +2403,8 @@
       <c r="D12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_BLOCK_CARD_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":5,"timing":"NEXT_CARD"},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_ATTACK_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":5,"timing":"NEXT_CARD"},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+      <c r="E12" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>47</v>
@@ -2450,10 +2429,8 @@
       <c r="D13" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_CARD_DAMAGE_DEALT","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.amount","cmp":"&gt;=","rhs":10},{"lhs":"@heavyHitRewarded","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"heavyHitRewarded","value":1,"scope":"TURN"},"children":[],"elseEffects":[]},{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+      <c r="E13" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>47</v>
@@ -2478,10 +2455,8 @@
       <c r="D14" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_ATTACK_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.requiredDiceCount","cmp":"&gt;=","rhs":2}]},"children":[{"type":210034,"target":"SELF","params":{"name":"heavyAttackCount","operator":"ADD","value":1,"scope":"TURN"},"children":[],"elseEffects":[]},{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@heavyAttackCount","cmp":"&gt;=","rhs":2},{"lhs":"@heavyAttackRewarded","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"heavyAttackRewarded","value":1,"scope":"TURN"},"children":[],"elseEffects":[]},{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+      <c r="E14" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>47</v>
@@ -2506,10 +2481,8 @@
       <c r="D15" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210036,"target":"SELF","params":{"kind":"DAMAGE","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_ENERGY_SPENT","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210034,"target":"SELF","params":{"name":"spentEnergy","operator":"ADD","value":"@event.spent","scope":"TURN"},"children":[],"elseEffects":[]},{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@spentEnergy","cmp":"&gt;=","rhs":3},{"lhs":"@energyDamageTriggered","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"energyDamageTriggered","value":1,"scope":"TURN"},"children":[],"elseEffects":[]},{"type":210001,"target":"ENEMY","params":{"amount":8,"hits":1,"damageKind":"SPECIAL","ignoreBlock":false},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+      <c r="E15" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>47</v>
@@ -2534,10 +2507,8 @@
       <c r="D16" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210039,"target":"SELF","params":{"amount":6},"children":[],"elseEffects":[]}]</t>
-        </is>
+      <c r="E16" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>73</v>
@@ -2562,10 +2533,8 @@
       <c r="D17" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_DAMAGE_TAKEN","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@hitGuardScheduled","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"hitGuardScheduled","value":1,"scope":"TURN"},"children":[],"elseEffects":[]},{"type":210023,"target":"SELF","params":{"when":"NEXT_TURN_START","times":1,"capture":{}},"children":[{"type":210002,"target":"SELF","params":{"amount":5,"scale":false},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+      <c r="E17" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>73</v>
@@ -2590,10 +2559,8 @@
       <c r="D18" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_HAND_READY","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210038,"target":"SELF","params":{"count":1},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_BLOCK_CARD_PLAYED","scope":"COMBAT","limit":0,"filter":{"type":"SKILL"}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@blockSkillDrawn","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"blockSkillDrawn","value":1,"scope":"TURN"},"children":[],"elseEffects":[]},{"type":210038,"target":"SELF","params":{"count":1},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+      <c r="E18" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>73</v>
@@ -2618,10 +2585,8 @@
       <c r="D19" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210036,"target":"SELF","params":{"kind":"BLOCK","amount":2,"timing":"COMBAT"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_END","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210002,"target":"SELF","params":{"amount":"min(@self.energy, 2) * 3","scale":false},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+      <c r="E19" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>73</v>
@@ -2646,10 +2611,8 @@
       <c r="D20" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":12,"duration":"RUN"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@self.hp","cmp":"&lt;","rhs":"@self.maxHp * 0.5"},{"lhs":"@lowHpTriggered","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"lowHpTriggered","value":1,"scope":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":12,"scale":false},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_HP_LOSS","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@self.hp","cmp":"&lt;","rhs":"@self.maxHp * 0.5"},{"lhs":"@lowHpTriggered","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"lowHpTriggered","value":1,"scope":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":12,"scale":false},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+      <c r="E20" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>73</v>
@@ -2674,10 +2637,8 @@
       <c r="D21" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":4,"scale":false},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+      <c r="E21" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>73</v>
@@ -2702,10 +2663,8 @@
       <c r="D22" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210015,"target":"SELF","params":{"stat":"MAX_HP","amount":6,"duration":"RUN"},"children":[],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_ENERGY_SPENT","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.current","cmp":"==","rhs":0},{"lhs":"@emptyEnergyGuarded","cmp":"==","rhs":0}]},"children":[{"type":210033,"target":"SELF","params":{"name":"emptyEnergyGuarded","value":1,"scope":"COMBAT"},"children":[],"elseEffects":[]},{"type":210002,"target":"SELF","params":{"amount":10,"scale":false},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+      <c r="E22" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>73</v>
@@ -2730,10 +2689,8 @@
       <c r="D23" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":2},"children":[],"elseEffects":[]}],"elseEffects":[]},{"type":210022,"target":"SELF","params":{"event":"ON_CARD_PLAYED","scope":"COMBAT","limit":0,"filter":{}},"children":[{"type":210019,"target":"SELF","params":{},"condition":{"op":"AND","rules":[{"lhs":"@event.cardCount","cmp":"==","rhs":3}]},"children":[{"type":210040,"target":"SELF","params":{"count":1,"scope":"TURN"},"children":[],"elseEffects":[]}],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+      <c r="E23" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>73</v>
@@ -2758,10 +2715,8 @@
       <c r="D24" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":1},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+      <c r="E24" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>47</v>
@@ -2786,10 +2741,8 @@
       <c r="D25" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>[{"type":210022,"target":"SELF","params":{"event":"ON_TURN_START","scope":"COMBAT","limit":1,"filter":{}},"children":[{"type":210037,"target":"SELF","params":{"amount":3},"children":[],"elseEffects":[]}],"elseEffects":[]}]</t>
-        </is>
+      <c r="E25" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>73</v>
